--- a/Experiments/outputs/scenario_3.xlsx
+++ b/Experiments/outputs/scenario_3.xlsx
@@ -530,55 +530,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2817.892855541199</v>
+        <v>2945.848454820575</v>
       </c>
       <c r="D2" t="n">
-        <v>3.744457960128784</v>
+        <v>4.987133979797363</v>
       </c>
       <c r="E2" t="n">
-        <v>788</v>
+        <v>757</v>
       </c>
       <c r="F2" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G2" t="n">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="H2" t="n">
-        <v>4998.617485004558</v>
+        <v>4727.653038548395</v>
       </c>
       <c r="I2" t="n">
-        <v>6.983359813690186</v>
+        <v>37.73264002799988</v>
       </c>
       <c r="J2" t="n">
-        <v>887</v>
+        <v>836</v>
       </c>
       <c r="K2" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L2" t="n">
-        <v>1033</v>
+        <v>1140</v>
       </c>
       <c r="M2" t="n">
-        <v>11607.34312355205</v>
+        <v>10793.62157061547</v>
       </c>
       <c r="N2" t="n">
-        <v>6.194269180297852</v>
+        <v>4.351142883300781</v>
       </c>
       <c r="O2" t="n">
-        <v>2783</v>
+        <v>3055</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q2" t="n">
-        <v>8223</v>
+        <v>8927</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7572318810991712</v>
+        <v>0.7270750659963524</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5693573084040187</v>
+        <v>0.5619956649750492</v>
       </c>
     </row>
     <row r="3">
@@ -591,55 +591,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2918.818860174591</v>
+        <v>2823.000034397603</v>
       </c>
       <c r="D3" t="n">
-        <v>2.387104034423828</v>
+        <v>5.766876220703125</v>
       </c>
       <c r="E3" t="n">
         <v>785</v>
       </c>
       <c r="F3" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G3" t="n">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="H3" t="n">
-        <v>4991.916405644711</v>
+        <v>4774.59770965262</v>
       </c>
       <c r="I3" t="n">
-        <v>5.980291128158569</v>
+        <v>36.50808691978455</v>
       </c>
       <c r="J3" t="n">
-        <v>932</v>
+        <v>879</v>
       </c>
       <c r="K3" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="L3" t="n">
-        <v>1059</v>
+        <v>1187</v>
       </c>
       <c r="M3" t="n">
-        <v>11609.65499100422</v>
+        <v>10848.84633315501</v>
       </c>
       <c r="N3" t="n">
-        <v>5.603398084640503</v>
+        <v>4.846476078033447</v>
       </c>
       <c r="O3" t="n">
-        <v>2766</v>
+        <v>3076</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q3" t="n">
-        <v>8150</v>
+        <v>9087</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7485869422961968</v>
+        <v>0.7397879970176855</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5700202624873252</v>
+        <v>0.5598981160733156</v>
       </c>
     </row>
     <row r="4">
@@ -652,55 +652,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2724.047631393716</v>
+        <v>3006.653909869086</v>
       </c>
       <c r="D4" t="n">
-        <v>2.254290819168091</v>
+        <v>5.862594127655029</v>
       </c>
       <c r="E4" t="n">
-        <v>754</v>
+        <v>817</v>
       </c>
       <c r="F4" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G4" t="n">
-        <v>416</v>
+        <v>531</v>
       </c>
       <c r="H4" t="n">
-        <v>4801.317734728951</v>
+        <v>4952.210854356727</v>
       </c>
       <c r="I4" t="n">
-        <v>4.441963195800781</v>
+        <v>45.76197695732117</v>
       </c>
       <c r="J4" t="n">
-        <v>832</v>
+        <v>926</v>
       </c>
       <c r="K4" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L4" t="n">
-        <v>978</v>
+        <v>1238</v>
       </c>
       <c r="M4" t="n">
-        <v>11453.76398264754</v>
+        <v>11012.65650400881</v>
       </c>
       <c r="N4" t="n">
-        <v>6.249433279037476</v>
+        <v>4.252080917358398</v>
       </c>
       <c r="O4" t="n">
-        <v>2809</v>
+        <v>3112</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>8323</v>
+        <v>9069</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7621700922490939</v>
+        <v>0.726981958551544</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5808087418247007</v>
+        <v>0.5503164152487612</v>
       </c>
     </row>
     <row r="5">
@@ -713,55 +713,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2788.39959011545</v>
+        <v>2583.796023432308</v>
       </c>
       <c r="D5" t="n">
-        <v>1.456748962402344</v>
+        <v>5.055294990539551</v>
       </c>
       <c r="E5" t="n">
-        <v>766</v>
+        <v>730</v>
       </c>
       <c r="F5" t="n">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="G5" t="n">
-        <v>434</v>
+        <v>395</v>
       </c>
       <c r="H5" t="n">
-        <v>5018.430323061647</v>
+        <v>4736.861712647791</v>
       </c>
       <c r="I5" t="n">
-        <v>3.44707202911377</v>
+        <v>36.08407616615295</v>
       </c>
       <c r="J5" t="n">
-        <v>860</v>
+        <v>813</v>
       </c>
       <c r="K5" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L5" t="n">
-        <v>1015</v>
+        <v>1149</v>
       </c>
       <c r="M5" t="n">
-        <v>11602.1115217363</v>
+        <v>10663.80397129248</v>
       </c>
       <c r="N5" t="n">
-        <v>4.926249265670776</v>
+        <v>4.841329336166382</v>
       </c>
       <c r="O5" t="n">
-        <v>2810</v>
+        <v>3066</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>8206</v>
+        <v>9051</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7596644727219312</v>
+        <v>0.7577040959878837</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5674554313962825</v>
+        <v>0.5558000010690677</v>
       </c>
     </row>
     <row r="6">
@@ -774,55 +774,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2830.062386679827</v>
+        <v>2897.645840349159</v>
       </c>
       <c r="D6" t="n">
-        <v>1.423961877822876</v>
+        <v>4.588386058807373</v>
       </c>
       <c r="E6" t="n">
-        <v>794</v>
+        <v>754</v>
       </c>
       <c r="F6" t="n">
         <v>124</v>
       </c>
       <c r="G6" t="n">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="H6" t="n">
-        <v>4966.631169855684</v>
+        <v>4715.663566077988</v>
       </c>
       <c r="I6" t="n">
-        <v>3.449457883834839</v>
+        <v>36.7991259098053</v>
       </c>
       <c r="J6" t="n">
-        <v>886</v>
+        <v>854</v>
       </c>
       <c r="K6" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="L6" t="n">
-        <v>1024</v>
+        <v>1158</v>
       </c>
       <c r="M6" t="n">
-        <v>11582.98099530099</v>
+        <v>10823.04768192367</v>
       </c>
       <c r="N6" t="n">
-        <v>4.599507093429565</v>
+        <v>4.572407007217407</v>
       </c>
       <c r="O6" t="n">
-        <v>2800</v>
+        <v>3046</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q6" t="n">
-        <v>8252</v>
+        <v>8891</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7556706354065561</v>
+        <v>0.7322708052752351</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5712130433546806</v>
+        <v>0.5642943000284525</v>
       </c>
     </row>
     <row r="7">
@@ -835,55 +835,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2823.172488899461</v>
+        <v>2697.978983279279</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1704261302948</v>
+        <v>4.786269903182983</v>
       </c>
       <c r="E7" t="n">
-        <v>715</v>
+        <v>758</v>
       </c>
       <c r="F7" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="G7" t="n">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="H7" t="n">
-        <v>4949.179402120195</v>
+        <v>4956.543145432117</v>
       </c>
       <c r="I7" t="n">
-        <v>3.52975606918335</v>
+        <v>43.68239998817444</v>
       </c>
       <c r="J7" t="n">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="K7" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L7" t="n">
-        <v>1036</v>
+        <v>1250</v>
       </c>
       <c r="M7" t="n">
-        <v>11351.11044035422</v>
+        <v>10823.43212471257</v>
       </c>
       <c r="N7" t="n">
-        <v>4.730081081390381</v>
+        <v>4.159972190856934</v>
       </c>
       <c r="O7" t="n">
-        <v>2733</v>
+        <v>3017</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Q7" t="n">
-        <v>8114</v>
+        <v>8858</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7512866689356815</v>
+        <v>0.7507279620556657</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5639916087394043</v>
+        <v>0.5420543975034404</v>
       </c>
     </row>
     <row r="8">
@@ -896,55 +896,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2858.715820565669</v>
+        <v>3082.616941657004</v>
       </c>
       <c r="D8" t="n">
-        <v>1.160587072372437</v>
+        <v>4.968008041381836</v>
       </c>
       <c r="E8" t="n">
-        <v>727</v>
+        <v>706</v>
       </c>
       <c r="F8" t="n">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="G8" t="n">
-        <v>407</v>
+        <v>441</v>
       </c>
       <c r="H8" t="n">
-        <v>5035.347217442298</v>
+        <v>4808.151423463323</v>
       </c>
       <c r="I8" t="n">
-        <v>3.49338698387146</v>
+        <v>41.03238916397095</v>
       </c>
       <c r="J8" t="n">
-        <v>891</v>
+        <v>861</v>
       </c>
       <c r="K8" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="L8" t="n">
-        <v>1025</v>
+        <v>1186</v>
       </c>
       <c r="M8" t="n">
-        <v>11510.01239148921</v>
+        <v>10836.05106433527</v>
       </c>
       <c r="N8" t="n">
-        <v>5.541157722473145</v>
+        <v>4.507456064224243</v>
       </c>
       <c r="O8" t="n">
-        <v>2793</v>
+        <v>3072</v>
       </c>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
-        <v>8303</v>
+        <v>8907</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7516322551764172</v>
+        <v>0.7155221100975768</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5625246049982051</v>
+        <v>0.5562819522613356</v>
       </c>
     </row>
     <row r="9">
@@ -957,55 +957,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2643.484472120039</v>
+        <v>2881.046491806977</v>
       </c>
       <c r="D9" t="n">
-        <v>1.652657985687256</v>
+        <v>6.352428197860718</v>
       </c>
       <c r="E9" t="n">
-        <v>719</v>
+        <v>796</v>
       </c>
       <c r="F9" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="G9" t="n">
-        <v>365</v>
+        <v>484</v>
       </c>
       <c r="H9" t="n">
-        <v>4845.842649815178</v>
+        <v>5026.418149421001</v>
       </c>
       <c r="I9" t="n">
-        <v>3.702788829803467</v>
+        <v>43.69917678833008</v>
       </c>
       <c r="J9" t="n">
-        <v>888</v>
+        <v>922</v>
       </c>
       <c r="K9" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="L9" t="n">
-        <v>1022</v>
+        <v>1257</v>
       </c>
       <c r="M9" t="n">
-        <v>11494.10918700253</v>
+        <v>10888.2063446182</v>
       </c>
       <c r="N9" t="n">
-        <v>4.77951192855835</v>
+        <v>4.334415197372437</v>
       </c>
       <c r="O9" t="n">
-        <v>2772</v>
+        <v>3084</v>
       </c>
       <c r="P9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="n">
-        <v>8217</v>
+        <v>9035</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7700139759321866</v>
+        <v>0.7353975117094457</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5784064192382277</v>
+        <v>0.5383612332158413</v>
       </c>
     </row>
     <row r="10">
@@ -1018,55 +1018,55 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2847.366720906286</v>
+        <v>2955.032649975597</v>
       </c>
       <c r="D10" t="n">
-        <v>1.345741033554077</v>
+        <v>5.52300500869751</v>
       </c>
       <c r="E10" t="n">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="F10" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G10" t="n">
-        <v>436</v>
+        <v>483</v>
       </c>
       <c r="H10" t="n">
-        <v>4860.794602626648</v>
+        <v>4761.058046004091</v>
       </c>
       <c r="I10" t="n">
-        <v>3.776220798492432</v>
+        <v>39.20258498191833</v>
       </c>
       <c r="J10" t="n">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="K10" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L10" t="n">
-        <v>1000</v>
+        <v>1161</v>
       </c>
       <c r="M10" t="n">
-        <v>11502.20281556276</v>
+        <v>10703.5355835757</v>
       </c>
       <c r="N10" t="n">
-        <v>4.408215045928955</v>
+        <v>4.271543741226196</v>
       </c>
       <c r="O10" t="n">
-        <v>2805</v>
+        <v>3067</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>8292</v>
+        <v>8977</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7524503117738692</v>
+        <v>0.7239199489830239</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5774031565458163</v>
+        <v>0.5551882825232241</v>
       </c>
     </row>
     <row r="11">
@@ -1079,55 +1079,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2725.702569264488</v>
+        <v>2823.2689897051</v>
       </c>
       <c r="D11" t="n">
-        <v>1.300994873046875</v>
+        <v>5.852980375289917</v>
       </c>
       <c r="E11" t="n">
-        <v>764</v>
+        <v>747</v>
       </c>
       <c r="F11" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G11" t="n">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="H11" t="n">
-        <v>5087.27116252517</v>
+        <v>4622.064721849209</v>
       </c>
       <c r="I11" t="n">
-        <v>4.439728260040283</v>
+        <v>39.17469525337219</v>
       </c>
       <c r="J11" t="n">
-        <v>867</v>
+        <v>838</v>
       </c>
       <c r="K11" t="n">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="L11" t="n">
-        <v>1017</v>
+        <v>1147</v>
       </c>
       <c r="M11" t="n">
-        <v>11590.41367076392</v>
+        <v>10797.90480755585</v>
       </c>
       <c r="N11" t="n">
-        <v>5.556934833526611</v>
+        <v>4.589543342590332</v>
       </c>
       <c r="O11" t="n">
-        <v>2801</v>
+        <v>3049</v>
       </c>
       <c r="P11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>8290</v>
+        <v>8875</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7648312953540305</v>
+        <v>0.7385354807231204</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5610794138126849</v>
+        <v>0.5719480024851756</v>
       </c>
     </row>
     <row r="12">
@@ -1140,55 +1140,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2899.45039893753</v>
+        <v>2771.268361664569</v>
       </c>
       <c r="D12" t="n">
-        <v>1.77579402923584</v>
+        <v>4.747514009475708</v>
       </c>
       <c r="E12" t="n">
-        <v>782</v>
+        <v>731</v>
       </c>
       <c r="F12" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G12" t="n">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="H12" t="n">
-        <v>4638.724253001651</v>
+        <v>4815.95859881198</v>
       </c>
       <c r="I12" t="n">
-        <v>5.516264915466309</v>
+        <v>44.21343088150024</v>
       </c>
       <c r="J12" t="n">
-        <v>843</v>
+        <v>833</v>
       </c>
       <c r="K12" t="n">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="L12" t="n">
-        <v>975</v>
+        <v>1147</v>
       </c>
       <c r="M12" t="n">
-        <v>11426.54473108621</v>
+        <v>10851.73324738391</v>
       </c>
       <c r="N12" t="n">
-        <v>5.799504041671753</v>
+        <v>4.675893068313599</v>
       </c>
       <c r="O12" t="n">
-        <v>2760</v>
+        <v>3091</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>8196</v>
+        <v>9046</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7462530916236209</v>
+        <v>0.7446243564517534</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5940396364631662</v>
+        <v>0.5562037428469787</v>
       </c>
     </row>
     <row r="13">
@@ -1201,55 +1201,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2908.788111558844</v>
+        <v>2827.4401600137</v>
       </c>
       <c r="D13" t="n">
-        <v>2.805865049362183</v>
+        <v>4.562994003295898</v>
       </c>
       <c r="E13" t="n">
-        <v>809</v>
+        <v>731</v>
       </c>
       <c r="F13" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="G13" t="n">
-        <v>496</v>
+        <v>411</v>
       </c>
       <c r="H13" t="n">
-        <v>4766.727207050246</v>
+        <v>4861.867373933197</v>
       </c>
       <c r="I13" t="n">
-        <v>5.963098287582397</v>
+        <v>47.19732928276062</v>
       </c>
       <c r="J13" t="n">
-        <v>853</v>
+        <v>890</v>
       </c>
       <c r="K13" t="n">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="L13" t="n">
-        <v>1005</v>
+        <v>1206</v>
       </c>
       <c r="M13" t="n">
-        <v>11452.60009103047</v>
+        <v>10667.0838279114</v>
       </c>
       <c r="N13" t="n">
-        <v>9.535311698913574</v>
+        <v>5.000710964202881</v>
       </c>
       <c r="O13" t="n">
-        <v>2787</v>
+        <v>3070</v>
       </c>
       <c r="P13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q13" t="n">
-        <v>8292</v>
+        <v>9034</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7460150456282002</v>
+        <v>0.7349378512789555</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5837864616626678</v>
+        <v>0.5442177588206746</v>
       </c>
     </row>
     <row r="14">
@@ -1262,55 +1262,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2816.515904489987</v>
+        <v>2990.485616892721</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4665846824646</v>
+        <v>4.494575262069702</v>
       </c>
       <c r="E14" t="n">
-        <v>794</v>
+        <v>736</v>
       </c>
       <c r="F14" t="n">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="G14" t="n">
-        <v>471</v>
+        <v>444</v>
       </c>
       <c r="H14" t="n">
-        <v>4921.230398653277</v>
+        <v>4861.808960171716</v>
       </c>
       <c r="I14" t="n">
-        <v>8.168325901031494</v>
+        <v>46.18246984481812</v>
       </c>
       <c r="J14" t="n">
-        <v>964</v>
+        <v>884</v>
       </c>
       <c r="K14" t="n">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="L14" t="n">
-        <v>1070</v>
+        <v>1208</v>
       </c>
       <c r="M14" t="n">
-        <v>11530.30607969294</v>
+        <v>10877.39426704885</v>
       </c>
       <c r="N14" t="n">
-        <v>4.883273839950562</v>
+        <v>4.64731502532959</v>
       </c>
       <c r="O14" t="n">
-        <v>2769</v>
+        <v>3077</v>
       </c>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="n">
-        <v>8279</v>
+        <v>9011</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7557293028456193</v>
+        <v>0.7250733453735451</v>
       </c>
       <c r="S14" t="n">
-        <v>0.573191694596859</v>
+        <v>0.5530355119240545</v>
       </c>
     </row>
     <row r="15">
@@ -1323,55 +1323,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2742.089556068845</v>
+        <v>2833.878738353629</v>
       </c>
       <c r="D15" t="n">
-        <v>1.232059955596924</v>
+        <v>4.892966032028198</v>
       </c>
       <c r="E15" t="n">
-        <v>752</v>
+        <v>725</v>
       </c>
       <c r="F15" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G15" t="n">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="H15" t="n">
-        <v>4718.293551148463</v>
+        <v>4866.031094854563</v>
       </c>
       <c r="I15" t="n">
-        <v>4.599780082702637</v>
+        <v>42.57259273529053</v>
       </c>
       <c r="J15" t="n">
-        <v>856</v>
+        <v>882</v>
       </c>
       <c r="K15" t="n">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L15" t="n">
-        <v>1004</v>
+        <v>1206</v>
       </c>
       <c r="M15" t="n">
-        <v>11559.89487881963</v>
+        <v>10777.47894977895</v>
       </c>
       <c r="N15" t="n">
-        <v>4.836688995361328</v>
+        <v>4.669819355010986</v>
       </c>
       <c r="O15" t="n">
-        <v>2810</v>
+        <v>3070</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Q15" t="n">
-        <v>8326</v>
+        <v>8969</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7627928640516463</v>
+        <v>0.7370555069920361</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5918394067930967</v>
+        <v>0.5485000604010117</v>
       </c>
     </row>
     <row r="16">
@@ -1384,55 +1384,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2836.167119334863</v>
+        <v>2840.609411936325</v>
       </c>
       <c r="D16" t="n">
-        <v>1.302536010742188</v>
+        <v>6.625773191452026</v>
       </c>
       <c r="E16" t="n">
-        <v>777</v>
+        <v>820</v>
       </c>
       <c r="F16" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="G16" t="n">
-        <v>444</v>
+        <v>513</v>
       </c>
       <c r="H16" t="n">
-        <v>4865.053238530214</v>
+        <v>4900.097029700208</v>
       </c>
       <c r="I16" t="n">
-        <v>3.980499267578125</v>
+        <v>47.64279103279114</v>
       </c>
       <c r="J16" t="n">
-        <v>857</v>
+        <v>942</v>
       </c>
       <c r="K16" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="L16" t="n">
-        <v>996</v>
+        <v>1248</v>
       </c>
       <c r="M16" t="n">
-        <v>11625.4504281882</v>
+        <v>10763.98316085774</v>
       </c>
       <c r="N16" t="n">
-        <v>5.846681833267212</v>
+        <v>4.807401895523071</v>
       </c>
       <c r="O16" t="n">
-        <v>2781</v>
+        <v>3048</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q16" t="n">
-        <v>8183</v>
+        <v>8929</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7560380875688036</v>
+        <v>0.7361005336513395</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5815170114412141</v>
+        <v>0.5447691661652749</v>
       </c>
     </row>
     <row r="17">
@@ -1445,55 +1445,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2746.91434025032</v>
+        <v>2788.414561719962</v>
       </c>
       <c r="D17" t="n">
-        <v>1.524403810501099</v>
+        <v>4.881505012512207</v>
       </c>
       <c r="E17" t="n">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="F17" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G17" t="n">
-        <v>396</v>
+        <v>431</v>
       </c>
       <c r="H17" t="n">
-        <v>4876.272874239965</v>
+        <v>4679.808361771944</v>
       </c>
       <c r="I17" t="n">
-        <v>3.996714353561401</v>
+        <v>39.53181123733521</v>
       </c>
       <c r="J17" t="n">
-        <v>849</v>
+        <v>883</v>
       </c>
       <c r="K17" t="n">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="L17" t="n">
-        <v>1001</v>
+        <v>1180</v>
       </c>
       <c r="M17" t="n">
-        <v>11440.39000159928</v>
+        <v>10834.2796458323</v>
       </c>
       <c r="N17" t="n">
-        <v>5.752968072891235</v>
+        <v>4.298131942749023</v>
       </c>
       <c r="O17" t="n">
-        <v>2793</v>
+        <v>3104</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>8325</v>
+        <v>9037</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7598932956073768</v>
+        <v>0.7426303683427073</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5737669018662562</v>
+        <v>0.5680554208721981</v>
       </c>
     </row>
     <row r="18">
@@ -1506,55 +1506,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2757.114670096232</v>
+        <v>2781.446541016151</v>
       </c>
       <c r="D18" t="n">
-        <v>2.042353868484497</v>
+        <v>5.834893703460693</v>
       </c>
       <c r="E18" t="n">
-        <v>713</v>
+        <v>760</v>
       </c>
       <c r="F18" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G18" t="n">
-        <v>368</v>
+        <v>446</v>
       </c>
       <c r="H18" t="n">
-        <v>4906.218782724592</v>
+        <v>4931.26718792867</v>
       </c>
       <c r="I18" t="n">
-        <v>4.637819051742554</v>
+        <v>47.81765413284302</v>
       </c>
       <c r="J18" t="n">
-        <v>867</v>
+        <v>937</v>
       </c>
       <c r="K18" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="L18" t="n">
-        <v>1007</v>
+        <v>1265</v>
       </c>
       <c r="M18" t="n">
-        <v>11520.60427305565</v>
+        <v>10864.14431548841</v>
       </c>
       <c r="N18" t="n">
-        <v>6.480232954025269</v>
+        <v>4.935240030288696</v>
       </c>
       <c r="O18" t="n">
-        <v>2829</v>
+        <v>3051</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Q18" t="n">
-        <v>8188</v>
+        <v>8956</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7606796827016649</v>
+        <v>0.7439792347888092</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5741352913059221</v>
+        <v>0.5460970468793908</v>
       </c>
     </row>
     <row r="19">
@@ -1567,55 +1567,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2827.780297003897</v>
+        <v>2766.891485333919</v>
       </c>
       <c r="D19" t="n">
-        <v>1.539632081985474</v>
+        <v>5.437248229980469</v>
       </c>
       <c r="E19" t="n">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="F19" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G19" t="n">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="H19" t="n">
-        <v>4782.199630968047</v>
+        <v>4718.122748703522</v>
       </c>
       <c r="I19" t="n">
-        <v>4.187428951263428</v>
+        <v>44.92383623123169</v>
       </c>
       <c r="J19" t="n">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="K19" t="n">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="L19" t="n">
-        <v>1031</v>
+        <v>1190</v>
       </c>
       <c r="M19" t="n">
-        <v>11682.40085454343</v>
+        <v>10757.32283989504</v>
       </c>
       <c r="N19" t="n">
-        <v>7.566772937774658</v>
+        <v>4.728864908218384</v>
       </c>
       <c r="O19" t="n">
-        <v>2761</v>
+        <v>3053</v>
       </c>
       <c r="P19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="n">
-        <v>8144</v>
+        <v>8968</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7579452774979777</v>
+        <v>0.7427899555944798</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5906492432068712</v>
+        <v>0.5614036299807138</v>
       </c>
     </row>
     <row r="20">
@@ -1628,55 +1628,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2947.51422998205</v>
+        <v>2672.981131132205</v>
       </c>
       <c r="D20" t="n">
-        <v>2.533217191696167</v>
+        <v>5.111774921417236</v>
       </c>
       <c r="E20" t="n">
-        <v>818</v>
+        <v>740</v>
       </c>
       <c r="F20" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G20" t="n">
-        <v>492</v>
+        <v>405</v>
       </c>
       <c r="H20" t="n">
-        <v>5098.459794203075</v>
+        <v>4735.619739963354</v>
       </c>
       <c r="I20" t="n">
-        <v>5.00770092010498</v>
+        <v>42.33724594116211</v>
       </c>
       <c r="J20" t="n">
-        <v>922</v>
+        <v>894</v>
       </c>
       <c r="K20" t="n">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="L20" t="n">
-        <v>1055</v>
+        <v>1219</v>
       </c>
       <c r="M20" t="n">
-        <v>11560.62758147954</v>
+        <v>10677.29744836569</v>
       </c>
       <c r="N20" t="n">
-        <v>6.890326976776123</v>
+        <v>4.47270393371582</v>
       </c>
       <c r="O20" t="n">
-        <v>2774</v>
+        <v>3067</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q20" t="n">
-        <v>8241</v>
+        <v>9027</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7450385622053899</v>
+        <v>0.7496575192310163</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5589807077281033</v>
+        <v>0.5564776795940803</v>
       </c>
     </row>
     <row r="21">
@@ -1689,55 +1689,55 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2885.940833081942</v>
+        <v>2935.488799375943</v>
       </c>
       <c r="D21" t="n">
-        <v>1.83244800567627</v>
+        <v>6.155457973480225</v>
       </c>
       <c r="E21" t="n">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="F21" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G21" t="n">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="H21" t="n">
-        <v>4984.99774994523</v>
+        <v>4817.749879617175</v>
       </c>
       <c r="I21" t="n">
-        <v>4.674972772598267</v>
+        <v>46.62699699401855</v>
       </c>
       <c r="J21" t="n">
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="K21" t="n">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="L21" t="n">
-        <v>1051</v>
+        <v>1199</v>
       </c>
       <c r="M21" t="n">
-        <v>11582.9212797863</v>
+        <v>10774.14260082893</v>
       </c>
       <c r="N21" t="n">
-        <v>8.860997200012207</v>
+        <v>4.908569097518921</v>
       </c>
       <c r="O21" t="n">
-        <v>2763</v>
+        <v>3114</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q21" t="n">
-        <v>8194</v>
+        <v>9089</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7508451656217086</v>
+        <v>0.727543164395272</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5696251723091049</v>
+        <v>0.5528414595843095</v>
       </c>
     </row>
     <row r="22">
@@ -1750,55 +1750,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2974.496880142108</v>
+        <v>2941.608183609383</v>
       </c>
       <c r="D22" t="n">
-        <v>2.236171007156372</v>
+        <v>6.033199071884155</v>
       </c>
       <c r="E22" t="n">
-        <v>798</v>
+        <v>822</v>
       </c>
       <c r="F22" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G22" t="n">
-        <v>482</v>
+        <v>508</v>
       </c>
       <c r="H22" t="n">
-        <v>4743.784898790346</v>
+        <v>4971.953076209954</v>
       </c>
       <c r="I22" t="n">
-        <v>5.030762910842896</v>
+        <v>53.1262218952179</v>
       </c>
       <c r="J22" t="n">
-        <v>830</v>
+        <v>933</v>
       </c>
       <c r="K22" t="n">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="L22" t="n">
-        <v>986</v>
+        <v>1257</v>
       </c>
       <c r="M22" t="n">
-        <v>11462.80972316184</v>
+        <v>10822.79605356129</v>
       </c>
       <c r="N22" t="n">
-        <v>5.657577991485596</v>
+        <v>5.208021879196167</v>
       </c>
       <c r="O22" t="n">
-        <v>2765</v>
+        <v>3074</v>
       </c>
       <c r="P22" t="n">
         <v>8</v>
       </c>
       <c r="Q22" t="n">
-        <v>8269</v>
+        <v>8979</v>
       </c>
       <c r="R22" t="n">
-        <v>0.740508919542491</v>
+        <v>0.7282025671507103</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5861586283505155</v>
+        <v>0.5406036433095394</v>
       </c>
     </row>
     <row r="23">
@@ -1811,55 +1811,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2785.225396658782</v>
+        <v>2902.155352263092</v>
       </c>
       <c r="D23" t="n">
-        <v>1.340842962265015</v>
+        <v>5.220145225524902</v>
       </c>
       <c r="E23" t="n">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="F23" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G23" t="n">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="H23" t="n">
-        <v>4863.647685957332</v>
+        <v>4916.49455505887</v>
       </c>
       <c r="I23" t="n">
-        <v>4.237173080444336</v>
+        <v>42.02405500411987</v>
       </c>
       <c r="J23" t="n">
-        <v>887</v>
+        <v>841</v>
       </c>
       <c r="K23" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="L23" t="n">
-        <v>1039</v>
+        <v>1191</v>
       </c>
       <c r="M23" t="n">
-        <v>11585.24190744391</v>
+        <v>10848.79596866065</v>
       </c>
       <c r="N23" t="n">
-        <v>5.910392045974731</v>
+        <v>5.976302862167358</v>
       </c>
       <c r="O23" t="n">
-        <v>2753</v>
+        <v>3096</v>
       </c>
       <c r="P23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q23" t="n">
-        <v>8082</v>
+        <v>9073</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7595884989791037</v>
+        <v>0.7324905583396846</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5801859188773371</v>
+        <v>0.5468165712341403</v>
       </c>
     </row>
     <row r="24">
@@ -1872,55 +1872,55 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2945.142320557009</v>
+        <v>2943.706233298064</v>
       </c>
       <c r="D24" t="n">
-        <v>1.421640157699585</v>
+        <v>5.863003015518188</v>
       </c>
       <c r="E24" t="n">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="F24" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G24" t="n">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="H24" t="n">
-        <v>4872.394468786668</v>
+        <v>4835.337968016784</v>
       </c>
       <c r="I24" t="n">
-        <v>7.056703090667725</v>
+        <v>46.39610600471497</v>
       </c>
       <c r="J24" t="n">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="K24" t="n">
         <v>145</v>
       </c>
       <c r="L24" t="n">
-        <v>1020</v>
+        <v>1198</v>
       </c>
       <c r="M24" t="n">
-        <v>11517.54939559424</v>
+        <v>10861.44872099048</v>
       </c>
       <c r="N24" t="n">
-        <v>5.233025789260864</v>
+        <v>4.651885032653809</v>
       </c>
       <c r="O24" t="n">
-        <v>2779</v>
+        <v>3061</v>
       </c>
       <c r="P24" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q24" t="n">
-        <v>8266</v>
+        <v>8936</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7442908886777945</v>
+        <v>0.7289766486114182</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5769590994200133</v>
+        <v>0.5548164805425846</v>
       </c>
     </row>
     <row r="25">
@@ -1933,55 +1933,55 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2701.826222740059</v>
+        <v>2755.224279734317</v>
       </c>
       <c r="D25" t="n">
-        <v>1.260133028030396</v>
+        <v>5.161473035812378</v>
       </c>
       <c r="E25" t="n">
-        <v>719</v>
+        <v>744</v>
       </c>
       <c r="F25" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G25" t="n">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="H25" t="n">
-        <v>5082.131584394302</v>
+        <v>5005.409243531351</v>
       </c>
       <c r="I25" t="n">
-        <v>4.512715101242065</v>
+        <v>43.32061100006104</v>
       </c>
       <c r="J25" t="n">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="K25" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L25" t="n">
-        <v>1052</v>
+        <v>1236</v>
       </c>
       <c r="M25" t="n">
-        <v>11535.96908288209</v>
+        <v>10641.33881627127</v>
       </c>
       <c r="N25" t="n">
-        <v>5.50675892829895</v>
+        <v>4.382707834243774</v>
       </c>
       <c r="O25" t="n">
-        <v>2763</v>
+        <v>3067</v>
       </c>
       <c r="P25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q25" t="n">
-        <v>8224</v>
+        <v>9028</v>
       </c>
       <c r="R25" t="n">
-        <v>0.765791135245913</v>
+        <v>0.7410829288208165</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5594534323141053</v>
+        <v>0.5296259869220808</v>
       </c>
     </row>
     <row r="26">
@@ -1994,55 +1994,55 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2694.181514255784</v>
+        <v>2900.201197716362</v>
       </c>
       <c r="D26" t="n">
-        <v>1.666494131088257</v>
+        <v>5.769079685211182</v>
       </c>
       <c r="E26" t="n">
-        <v>758</v>
+        <v>798</v>
       </c>
       <c r="F26" t="n">
         <v>119</v>
       </c>
       <c r="G26" t="n">
-        <v>428</v>
+        <v>468</v>
       </c>
       <c r="H26" t="n">
-        <v>4821.080043191254</v>
+        <v>4754.598977640439</v>
       </c>
       <c r="I26" t="n">
-        <v>3.884115934371948</v>
+        <v>43.04948925971985</v>
       </c>
       <c r="J26" t="n">
-        <v>900</v>
+        <v>879</v>
       </c>
       <c r="K26" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="L26" t="n">
-        <v>1038</v>
+        <v>1191</v>
       </c>
       <c r="M26" t="n">
-        <v>11488.42908543482</v>
+        <v>10696.2774212546</v>
       </c>
       <c r="N26" t="n">
-        <v>4.549170970916748</v>
+        <v>4.84001898765564</v>
       </c>
       <c r="O26" t="n">
-        <v>2767</v>
+        <v>3081</v>
       </c>
       <c r="P26" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Q26" t="n">
-        <v>8224</v>
+        <v>9061</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7654873878560557</v>
+        <v>0.7288588278429126</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5803534140883123</v>
+        <v>0.5554903084139757</v>
       </c>
     </row>
     <row r="27">
@@ -2055,55 +2055,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2806.321955776247</v>
+        <v>2835.018808559386</v>
       </c>
       <c r="D27" t="n">
-        <v>2.232135057449341</v>
+        <v>5.243952035903931</v>
       </c>
       <c r="E27" t="n">
-        <v>837</v>
+        <v>757</v>
       </c>
       <c r="F27" t="n">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="G27" t="n">
-        <v>489</v>
+        <v>448</v>
       </c>
       <c r="H27" t="n">
-        <v>4924.069249042035</v>
+        <v>4700.687734705029</v>
       </c>
       <c r="I27" t="n">
-        <v>3.871367931365967</v>
+        <v>42.91984295845032</v>
       </c>
       <c r="J27" t="n">
-        <v>916</v>
+        <v>869</v>
       </c>
       <c r="K27" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="L27" t="n">
-        <v>1043</v>
+        <v>1182</v>
       </c>
       <c r="M27" t="n">
-        <v>11325.56468401526</v>
+        <v>10711.75414460644</v>
       </c>
       <c r="N27" t="n">
-        <v>5.379230976104736</v>
+        <v>5.164021968841553</v>
       </c>
       <c r="O27" t="n">
-        <v>2772</v>
+        <v>3061</v>
       </c>
       <c r="P27" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q27" t="n">
-        <v>8294</v>
+        <v>8978</v>
       </c>
       <c r="R27" t="n">
-        <v>0.7522135068693704</v>
+        <v>0.7353357096991562</v>
       </c>
       <c r="S27" t="n">
-        <v>0.5652252769354805</v>
+        <v>0.5611654570066932</v>
       </c>
     </row>
     <row r="28">
@@ -2116,55 +2116,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2835.095355096464</v>
+        <v>2765.359322009435</v>
       </c>
       <c r="D28" t="n">
-        <v>1.601316928863525</v>
+        <v>5.118242025375366</v>
       </c>
       <c r="E28" t="n">
-        <v>787</v>
+        <v>740</v>
       </c>
       <c r="F28" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G28" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H28" t="n">
-        <v>4790.385258887403</v>
+        <v>4534.997185025725</v>
       </c>
       <c r="I28" t="n">
-        <v>3.498024940490723</v>
+        <v>40.76889801025391</v>
       </c>
       <c r="J28" t="n">
-        <v>858</v>
+        <v>822</v>
       </c>
       <c r="K28" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L28" t="n">
-        <v>999</v>
+        <v>1129</v>
       </c>
       <c r="M28" t="n">
-        <v>11307.40438002754</v>
+        <v>10745.71737221876</v>
       </c>
       <c r="N28" t="n">
-        <v>5.428691148757935</v>
+        <v>4.861018896102905</v>
       </c>
       <c r="O28" t="n">
-        <v>2765</v>
+        <v>3048</v>
       </c>
       <c r="P28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q28" t="n">
-        <v>8164</v>
+        <v>8885</v>
       </c>
       <c r="R28" t="n">
-        <v>0.7492708972092532</v>
+        <v>0.7426547501464345</v>
       </c>
       <c r="S28" t="n">
-        <v>0.5763496999055996</v>
+        <v>0.5779716674151325</v>
       </c>
     </row>
     <row r="29">
@@ -2177,55 +2177,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3002.808769931875</v>
+        <v>2943.432804405851</v>
       </c>
       <c r="D29" t="n">
-        <v>1.398081064224243</v>
+        <v>5.16628098487854</v>
       </c>
       <c r="E29" t="n">
-        <v>837</v>
+        <v>737</v>
       </c>
       <c r="F29" t="n">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="G29" t="n">
-        <v>519</v>
+        <v>425</v>
       </c>
       <c r="H29" t="n">
-        <v>4724.539337517402</v>
+        <v>4920.830270561944</v>
       </c>
       <c r="I29" t="n">
-        <v>3.518321990966797</v>
+        <v>41.47394299507141</v>
       </c>
       <c r="J29" t="n">
-        <v>894</v>
+        <v>875</v>
       </c>
       <c r="K29" t="n">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="L29" t="n">
-        <v>1023</v>
+        <v>1190</v>
       </c>
       <c r="M29" t="n">
-        <v>11591.49207226807</v>
+        <v>10790.85170343075</v>
       </c>
       <c r="N29" t="n">
-        <v>4.77152681350708</v>
+        <v>4.285048961639404</v>
       </c>
       <c r="O29" t="n">
-        <v>2780</v>
+        <v>3073</v>
       </c>
       <c r="P29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q29" t="n">
-        <v>8183</v>
+        <v>9026</v>
       </c>
       <c r="R29" t="n">
-        <v>0.7409471747717526</v>
+        <v>0.7272288707785651</v>
       </c>
       <c r="S29" t="n">
-        <v>0.5924131847684586</v>
+        <v>0.5439812902815209</v>
       </c>
     </row>
     <row r="30">
@@ -2238,55 +2238,55 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2680.848576865642</v>
+        <v>2843.330065475665</v>
       </c>
       <c r="D30" t="n">
-        <v>1.297454833984375</v>
+        <v>5.510277986526489</v>
       </c>
       <c r="E30" t="n">
-        <v>768</v>
+        <v>712</v>
       </c>
       <c r="F30" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G30" t="n">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="H30" t="n">
-        <v>4956.479706967687</v>
+        <v>4682.486403002675</v>
       </c>
       <c r="I30" t="n">
-        <v>4.169450044631958</v>
+        <v>41.87334012985229</v>
       </c>
       <c r="J30" t="n">
-        <v>889</v>
+        <v>819</v>
       </c>
       <c r="K30" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L30" t="n">
-        <v>1039</v>
+        <v>1148</v>
       </c>
       <c r="M30" t="n">
-        <v>11441.98924976141</v>
+        <v>10701.61020838259</v>
       </c>
       <c r="N30" t="n">
-        <v>5.236701965332031</v>
+        <v>4.45097804069519</v>
       </c>
       <c r="O30" t="n">
-        <v>2787</v>
+        <v>3052</v>
       </c>
       <c r="P30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q30" t="n">
-        <v>8291</v>
+        <v>8966</v>
       </c>
       <c r="R30" t="n">
-        <v>0.7657008306556884</v>
+        <v>0.7343082012790487</v>
       </c>
       <c r="S30" t="n">
-        <v>0.5668166086529894</v>
+        <v>0.5624502937572073</v>
       </c>
     </row>
     <row r="31">
@@ -2299,55 +2299,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2724.025285294319</v>
+        <v>2909.749950056546</v>
       </c>
       <c r="D31" t="n">
-        <v>1.435738801956177</v>
+        <v>6.314247131347656</v>
       </c>
       <c r="E31" t="n">
-        <v>777</v>
+        <v>789</v>
       </c>
       <c r="F31" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G31" t="n">
-        <v>429</v>
+        <v>468</v>
       </c>
       <c r="H31" t="n">
-        <v>5185.330229457598</v>
+        <v>4928.508011012816</v>
       </c>
       <c r="I31" t="n">
-        <v>4.494720935821533</v>
+        <v>43.38852024078369</v>
       </c>
       <c r="J31" t="n">
-        <v>962</v>
+        <v>884</v>
       </c>
       <c r="K31" t="n">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="L31" t="n">
-        <v>1081</v>
+        <v>1204</v>
       </c>
       <c r="M31" t="n">
-        <v>11551.28650958237</v>
+        <v>10853.10484613605</v>
       </c>
       <c r="N31" t="n">
-        <v>5.662081956863403</v>
+        <v>5.203468084335327</v>
       </c>
       <c r="O31" t="n">
-        <v>2754</v>
+        <v>3088</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q31" t="n">
-        <v>8130</v>
+        <v>8971</v>
       </c>
       <c r="R31" t="n">
-        <v>0.7641799220342596</v>
+        <v>0.7318970017052325</v>
       </c>
       <c r="S31" t="n">
-        <v>0.5511036606047206</v>
+        <v>0.5458895789837066</v>
       </c>
     </row>
   </sheetData>
